--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20231.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -82,40 +82,61 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>MARQUEZ</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
     <t>ARIAS</t>
   </si>
   <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
     <t>AMALIA PAULINA</t>
   </si>
   <si>
-    <t>SERGIO</t>
-  </si>
-  <si>
     <t>ESMERALDA</t>
   </si>
   <si>
     <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>INGRID CRISTEL</t>
+  </si>
+  <si>
+    <t>AILYN</t>
   </si>
 </sst>
 </file>
@@ -539,7 +560,7 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -548,10 +569,10 @@
         <v>8</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>78.38</v>
+        <v>77.78</v>
       </c>
       <c r="H3">
         <v>7.5</v>
@@ -659,16 +680,19 @@
         <v>44</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>44</v>
       </c>
-      <c r="E2">
-        <v>44</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -679,19 +703,22 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -705,16 +732,19 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>88.89</v>
+      </c>
+      <c r="H4">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -728,16 +758,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>84.62</v>
+      </c>
+      <c r="H5">
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -793,16 +826,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G2">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -813,22 +846,22 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>78.38</v>
+        <v>75</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -854,7 +887,7 @@
         <v>88.89</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -871,16 +904,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>92.31</v>
+        <v>84.62</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -890,7 +923,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -922,16 +955,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920240</v>
+        <v>22330051920236</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -945,16 +978,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051420317</v>
+        <v>22330051920240</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -974,10 +1007,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -997,10 +1030,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1010,6 +1043,75 @@
       </c>
       <c r="G5">
         <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920390</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920057</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920366</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20231.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="37">
   <si>
     <t>Mat</t>
   </si>
@@ -82,9 +82,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -103,9 +100,6 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MARQUEZ</t>
   </si>
   <si>
@@ -116,9 +110,6 @@
   </si>
   <si>
     <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>KEVIN ALEXIS</t>
   </si>
   <si>
     <t>AMALIA PAULINA</t>
@@ -923,7 +914,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -955,16 +946,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920236</v>
+        <v>22330051920240</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -978,22 +969,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920240</v>
+        <v>20330051920126</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1001,22 +992,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920126</v>
+        <v>21330051920031</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1024,16 +1015,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920031</v>
+        <v>21330051920390</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1047,16 +1038,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920390</v>
+        <v>21330051920057</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1070,47 +1061,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920057</v>
+        <v>22330051920366</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920366</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20231.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20231.xlsx
@@ -852,7 +852,7 @@
         <v>75</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20231.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -82,52 +82,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>AMALIA PAULINA</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>AILYN</t>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>KEVIN ALEXIS</t>
   </si>
 </sst>
 </file>
@@ -826,7 +787,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -843,13 +804,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>75</v>
+        <v>86.11</v>
       </c>
       <c r="H3">
         <v>7.1</v>
@@ -869,16 +830,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>88.89</v>
+        <v>96.3</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -895,16 +856,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>84.62</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -914,7 +875,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -946,16 +907,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920240</v>
+        <v>22330051920236</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -965,121 +926,6 @@
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920126</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920031</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920390</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920057</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920366</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20231.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20231.xlsx
@@ -804,13 +804,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>86.11</v>
+        <v>88.89</v>
       </c>
       <c r="H3">
         <v>7.1</v>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20231.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20231.xlsx
@@ -787,7 +787,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -813,7 +813,7 @@
         <v>88.89</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -839,7 +839,7 @@
         <v>96.3</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -865,7 +865,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20231.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20231.xlsx
@@ -787,7 +787,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -813,7 +813,7 @@
         <v>88.89</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -839,7 +839,7 @@
         <v>96.3</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -865,7 +865,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
